--- a/AP/Template AP invoice.xlsx
+++ b/AP/Template AP invoice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\AP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF9C93E9-43D7-46BD-959E-6C05AD0C50FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE87753C-8551-41F6-87DB-ED7D5458C769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{741FD557-10E3-4BE6-AD8D-2BA066E5F42E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{741FD557-10E3-4BE6-AD8D-2BA066E5F42E}"/>
   </bookViews>
   <sheets>
     <sheet name="AP template H" sheetId="2" r:id="rId1"/>
@@ -161,6 +161,24 @@
 Type: long_x000D_
 Field Length: 6_x000D_
 Related Table: NNM1_x000D_
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{FF0A6603-6110-42C4-9ADA-8E51207D685B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Description: Object Type_x000D_
+Type: string_x000D_
+Field Length: 20_x000D_
+Related Table: ADP1_x000D_
 </t>
         </r>
       </text>
@@ -649,7 +667,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="347">
   <si>
     <t>DocNum</t>
   </si>
@@ -1684,13 +1702,19 @@
   </si>
   <si>
     <t>Claim RE</t>
+  </si>
+  <si>
+    <t>DocObjectCode</t>
+  </si>
+  <si>
+    <t>ObjType</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1733,6 +1757,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Phetsarath OT"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1821,7 +1859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1861,6 +1899,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2198,7 +2238,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="5" bestFit="1" customWidth="1"/>
@@ -2208,14 +2248,11 @@
     <col min="5" max="5" width="13.59765625" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.3984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.3984375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.09765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.796875" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="8.796875" style="5"/>
+    <col min="8" max="8" width="24.796875" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="8.796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2237,17 +2274,20 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -2269,17 +2309,20 @@
       <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -2299,16 +2342,19 @@
         <v>111</v>
       </c>
       <c r="H3" s="5">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5">
         <v>56</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K3" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -2328,16 +2374,19 @@
         <v>111</v>
       </c>
       <c r="H4" s="5">
+        <v>18</v>
+      </c>
+      <c r="I4" s="5">
         <v>57</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K4" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -2357,16 +2406,19 @@
         <v>111</v>
       </c>
       <c r="H5" s="5">
+        <v>18</v>
+      </c>
+      <c r="I5" s="5">
         <v>58</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K5" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -2386,16 +2438,19 @@
         <v>111</v>
       </c>
       <c r="H6" s="5">
+        <v>18</v>
+      </c>
+      <c r="I6" s="5">
         <v>59</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K6" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -2415,16 +2470,19 @@
         <v>111</v>
       </c>
       <c r="H7" s="5">
+        <v>18</v>
+      </c>
+      <c r="I7" s="5">
         <v>60</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K7" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -2444,16 +2502,19 @@
         <v>111</v>
       </c>
       <c r="H8" s="5">
+        <v>18</v>
+      </c>
+      <c r="I8" s="5">
         <v>61</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K8" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -2473,16 +2534,19 @@
         <v>111</v>
       </c>
       <c r="H9" s="5">
+        <v>18</v>
+      </c>
+      <c r="I9" s="5">
         <v>62</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K9" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -2502,16 +2566,19 @@
         <v>111</v>
       </c>
       <c r="H10" s="5">
+        <v>18</v>
+      </c>
+      <c r="I10" s="5">
         <v>63</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K10" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -2531,16 +2598,19 @@
         <v>111</v>
       </c>
       <c r="H11" s="5">
+        <v>18</v>
+      </c>
+      <c r="I11" s="5">
         <v>64</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="J11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K11" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -2560,16 +2630,19 @@
         <v>111</v>
       </c>
       <c r="H12" s="5">
+        <v>18</v>
+      </c>
+      <c r="I12" s="5">
         <v>65</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="J12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K12" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -2589,16 +2662,19 @@
         <v>111</v>
       </c>
       <c r="H13" s="5">
+        <v>18</v>
+      </c>
+      <c r="I13" s="5">
         <v>66</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K13" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -2618,16 +2694,19 @@
         <v>111</v>
       </c>
       <c r="H14" s="5">
+        <v>18</v>
+      </c>
+      <c r="I14" s="5">
         <v>67</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="J14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K14" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -2647,16 +2726,19 @@
         <v>111</v>
       </c>
       <c r="H15" s="5">
+        <v>18</v>
+      </c>
+      <c r="I15" s="5">
         <v>68</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -2676,12 +2758,15 @@
         <v>111</v>
       </c>
       <c r="H16" s="5">
+        <v>18</v>
+      </c>
+      <c r="I16" s="5">
         <v>69</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="J16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>344</v>
       </c>
     </row>
